--- a/docs/StructureDefinition-HospitalLocation12083.xlsx
+++ b/docs/StructureDefinition-HospitalLocation12083.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation12083.xlsx
+++ b/docs/StructureDefinition-HospitalLocation12083.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation12083.xlsx
+++ b/docs/StructureDefinition-HospitalLocation12083.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
